--- a/CardArchive/Tools/DataExport/Status.xlsx
+++ b/CardArchive/Tools/DataExport/Status.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="References" sheetId="1" r:id="rId1"/>
-    <sheet name="Enums" sheetId="2" r:id="rId2"/>
-    <sheet name="Status" sheetId="3" r:id="rId3"/>
+    <sheet name="Reference" sheetId="1" r:id="rId1"/>
+    <sheet name="Enum" sheetId="2" r:id="rId2"/>
+    <sheet name="_컬럼 설명" sheetId="3" r:id="rId3"/>
+    <sheet name="Status" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -13,30 +14,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">File</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -45,264 +25,587 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_StatusType</t>
-        </is>
-      </c>
-      <c r="B1"/>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enum</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!GenerateCsEnum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">AddAttack</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G4">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">AddHP</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">AddManaCost</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G6">
         <v>6</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">StoreValue</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G7">
         <v>7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Stealth</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G8">
         <v>10</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Invincibility</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G9">
         <v>12</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Shell</t>
         </is>
       </c>
-      <c r="B9">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G10">
         <v>13</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">Protection</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G11">
         <v>14</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Protected</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G12">
         <v>15</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">Armor</t>
         </is>
       </c>
-      <c r="B12">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G13">
         <v>16</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">SpellImmunity</t>
         </is>
       </c>
-      <c r="B13">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G14">
         <v>18</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">Deathtouch</t>
         </is>
       </c>
-      <c r="B14">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G15">
         <v>20</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">Fury</t>
         </is>
       </c>
-      <c r="B15">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G16">
         <v>22</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Intimidate</t>
         </is>
       </c>
-      <c r="B16">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G17">
         <v>23</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">Flying</t>
         </is>
       </c>
-      <c r="B17">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G18">
         <v>24</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t xml:space="preserve">Trample</t>
         </is>
       </c>
-      <c r="B18">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G19">
         <v>26</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">LifeSteal</t>
         </is>
       </c>
-      <c r="B19">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G20">
         <v>28</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Silenced</t>
         </is>
       </c>
-      <c r="B20">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G21">
         <v>30</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Paralysed</t>
         </is>
       </c>
-      <c r="B21">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G22">
         <v>32</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">Poisoned</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G23">
         <v>34</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Sleep</t>
         </is>
       </c>
-      <c r="B23">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G24">
         <v>36</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">MassShooting</t>
         </is>
       </c>
-      <c r="B24">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G25">
         <v>41</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Enumerator</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">Evasion</t>
         </is>
       </c>
-      <c r="B25">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="G26">
         <v>42</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -312,770 +615,1093 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TableName</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="C3"/>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bad_status</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effect</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hvalue</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9"/>
+    </row>
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+    </row>
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status_fx</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+    </row>
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+    </row>
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndTable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Table</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!AutoKey;!GenerateCsEnum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">bad_status</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">desc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">effect</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">hvalue</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">icon</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t xml:space="preserve">status_fx</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_Status</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bool</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_StatusType</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">path</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">path</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_attack</t>
-        </is>
-      </c>
-      <c r="B3" t="b">
-        <v>0</v>
-      </c>
+      <c r="A3"/>
+      <c r="B3"/>
       <c r="C3"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StatusType</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">add_attack</t>
+        </is>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4"/>
+      <c r="G4" t="inlineStr">
+        <is>
           <t xml:space="preserve">AddAttack</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="F3"/>
-      <c r="G3"/>
-      <c r="H3" t="inlineStr">
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">ATK Bonus</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_hp</t>
-        </is>
-      </c>
-      <c r="B4" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bonus HP.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AddHP</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4"/>
-      <c r="G4"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HP Bonus</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">add_mana_cost</t>
-        </is>
-      </c>
-      <c r="B5" t="b">
-        <v>0</v>
-      </c>
+      <c r="A5"/>
+      <c r="B5"/>
       <c r="C5"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AddManaCost</t>
+          <t xml:space="preserve">add_hp</t>
         </is>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5"/>
-      <c r="G5"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mana Bonus</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus HP.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AddHP</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HP Bonus</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">armor</t>
-        </is>
-      </c>
-      <c r="B6" t="b">
-        <v>0</v>
-      </c>
+      <c r="A6"/>
+      <c r="B6"/>
       <c r="C6"/>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">add_mana_cost</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AddManaCost</t>
+        </is>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mana Bonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">armor</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7"/>
+      <c r="G7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Armor</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6" t="inlineStr">
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve">Armor</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deathtouch</t>
-        </is>
-      </c>
-      <c r="B7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kill any creature it damages.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deathtouch</t>
-        </is>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Deathtouch</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">evasion</t>
-        </is>
-      </c>
-      <c r="B8" t="b">
-        <v>0</v>
-      </c>
+      <c r="A8"/>
+      <c r="B8"/>
       <c r="C8"/>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">deathtouch</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kill any creature it damages.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deathtouch</t>
+        </is>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deathtouch</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evasion</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Evasion</t>
         </is>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8"/>
-      <c r="G8"/>
-      <c r="H8" t="inlineStr">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t xml:space="preserve">Evasion</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">flying</t>
         </is>
       </c>
-      <c r="B9" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ignores Taunt.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">Flying</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="H10">
         <v>1</v>
       </c>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9" t="inlineStr">
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t xml:space="preserve">Flying</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">fury</t>
         </is>
       </c>
-      <c r="B10" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">Can attack twice per turn</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">Fury</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="H11">
         <v>1</v>
       </c>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10" t="inlineStr">
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Fury</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">intimidate</t>
         </is>
       </c>
-      <c r="B11" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t xml:space="preserve">When attacking, target does not counter-attack.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">Intimidate</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="H12">
         <v>1</v>
       </c>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11" t="inlineStr">
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Intimidate</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">invicibility</t>
         </is>
       </c>
-      <c r="B12" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t xml:space="preserve">Cannot be destroyed.</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">Invincibility</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="F12"/>
-      <c r="G12"/>
-      <c r="H12" t="inlineStr">
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Invincible</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lifesteal</t>
-        </is>
-      </c>
-      <c r="B13" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heal yourself when dealing damage.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LifeSteal</t>
-        </is>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13"/>
-      <c r="G13"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Life Steal</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mass_shooting</t>
-        </is>
-      </c>
-      <c r="B14" t="b">
-        <v>0</v>
-      </c>
+      <c r="A14"/>
+      <c r="B14"/>
       <c r="C14"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MassShooting</t>
+          <t xml:space="preserve">lifesteal</t>
         </is>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mass Shooting</t>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heal yourself when dealing damage.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LifeSteal</t>
+        </is>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Life Steal</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">paralysed</t>
-        </is>
-      </c>
-      <c r="B15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cannot perform any actions.</t>
-        </is>
-      </c>
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paralysed</t>
+          <t xml:space="preserve">mass_shooting</t>
         </is>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F15"/>
       <c r="G15" t="inlineStr">
         <is>
+          <t xml:space="preserve">MassShooting</t>
+        </is>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mass Shooting</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paralysed</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cannot perform any actions.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paralysed</t>
+        </is>
+      </c>
+      <c r="H16">
+        <v>-1</v>
+      </c>
+      <c r="I16"/>
+      <c r="J16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/StunFX.prefab</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Paralysed</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">poisoned</t>
         </is>
       </c>
-      <c r="B16" t="b">
+      <c r="E17">
         <v>1</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">Each turn, will lose hp.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">Poisoned</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="H17">
         <v>-1</v>
       </c>
-      <c r="F16"/>
-      <c r="G16" t="inlineStr">
+      <c r="I17"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/Poisoned.prefab</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t xml:space="preserve">Poisoned</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">protected</t>
         </is>
       </c>
-      <c r="B17" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">Cannot be attacked. Protected by Taunt.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">Protected</t>
         </is>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17"/>
-      <c r="G17" t="inlineStr">
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/Shield.prefab</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t xml:space="preserve">Protected</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">shell</t>
         </is>
       </c>
-      <c r="B18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">On the first hit, takes no damage.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">Shell</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="H19">
         <v>1</v>
       </c>
-      <c r="F18"/>
-      <c r="G18" t="inlineStr">
+      <c r="I19"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/Shell.prefab</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t xml:space="preserve">Shell</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">silenced</t>
         </is>
       </c>
-      <c r="B19" t="b">
+      <c r="E20">
         <v>1</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">Cannot use abilities.</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">Silenced</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="H20">
         <v>-1</v>
       </c>
-      <c r="F19"/>
-      <c r="G19" t="inlineStr">
+      <c r="I20"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/Silenced.prefab</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t xml:space="preserve">Silenced</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">sleep</t>
         </is>
       </c>
-      <c r="B20" t="b">
+      <c r="E21">
         <v>1</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">Does not unexhaust.
 Removed if attacked.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">Sleep</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="H21">
         <v>-1</v>
       </c>
-      <c r="F20"/>
-      <c r="G20" t="inlineStr">
+      <c r="I21"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/Zzz.prefab</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t xml:space="preserve">Sleep</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">spell_immunity</t>
         </is>
       </c>
-      <c r="B21" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Cannot be targeted or damaged by spells and traps.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">SpellImmunity</t>
         </is>
       </c>
-      <c r="E21">
+      <c r="H22">
         <v>1</v>
       </c>
-      <c r="F21"/>
-      <c r="G21" t="inlineStr">
+      <c r="I22"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/Immune.prefab</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t xml:space="preserve">Spell Immunity</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">stealth</t>
         </is>
       </c>
-      <c r="B22" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Cannot be targeted.</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">Stealth</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="H23">
         <v>1</v>
       </c>
-      <c r="F22"/>
-      <c r="G22" t="inlineStr">
+      <c r="I23"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Prefabs/FX/Hidden.prefab</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t xml:space="preserve">Stealth</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">taunt</t>
         </is>
       </c>
-      <c r="B23" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">도발</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">Protection</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="H24">
         <v>1</v>
       </c>
-      <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23" t="inlineStr">
+      <c r="I24"/>
+      <c r="J24"/>
+      <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">도발</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">trample</t>
         </is>
       </c>
-      <c r="B24" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Extra damage is dealt to player.</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">Trample</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="H25">
         <v>1</v>
       </c>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24" t="inlineStr">
+      <c r="I25"/>
+      <c r="J25"/>
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">Trample</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndTable</t>
         </is>

--- a/CardArchive/Tools/DataExport/Status.xlsx
+++ b/CardArchive/Tools/DataExport/Status.xlsx
@@ -8,6 +8,44 @@
     <sheet name="Status" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font/>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -640,37 +678,37 @@
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Type</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">설명</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">비고</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndField</t>
         </is>
